--- a/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64986_completo.xlsx
+++ b/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64986_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf2c33b76bf794afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4d42f4b459af45a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: La Libertad / Prov: Viru / Dist.: Chao</x:t>
+          <x:t>Dpto: La Libertad / Prov: Virú / Dist.: Chao</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,141 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.2908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.0070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.1962</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.0814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.8787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.8787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.6354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.7030</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.6895</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64986_completo.xlsx
+++ b/1376_Cuenca_Santa/_raw_reportes_xlsx/IDConfig_64986_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4d42f4b459af45a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R697e6e3f3ea34938"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.9819</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.2131</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.0514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.4687</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.5212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.9173</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.1392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.0123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.3381</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.3892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.8216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.6272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.3970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.1991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.8483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.6997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.1010</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.1147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.6759</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.5070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.5452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.5273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.3583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.5948</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.1489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.6552</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.1005</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.2895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.3443</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.2243</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.1115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.5526</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.1765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.2299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.3516</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.7367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.4117</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.4027</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.3381</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.1063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     53.3957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     51.4936</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.7440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.8313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.8516</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.8854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.3583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
